--- a/utils/monday_sprint_sprint_2024-27.xlsx
+++ b/utils/monday_sprint_sprint_2024-27.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="130">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -87,7 +87,7 @@
     <t>09/01/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>21/01/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -108,7 +108,7 @@
     <t>5822611271</t>
   </si>
   <si>
-    <t>18631</t>
+    <t>5539935026</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -123,6 +123,9 @@
     <t>20/11/2023</t>
   </si>
   <si>
+    <t>20/01/2024</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
@@ -132,7 +135,7 @@
     <t>Novembro</t>
   </si>
   <si>
-    <t>23840</t>
+    <t>5813969320</t>
   </si>
   <si>
     <t>Atualização - Recibo de Embarque - Migração EV3</t>
@@ -144,7 +147,10 @@
     <t>08/01/2024</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>17/01/2024</t>
+  </si>
+  <si>
+    <t>5894586764</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -156,7 +162,10 @@
     <t>19/01/2024</t>
   </si>
   <si>
-    <t>23467</t>
+    <t>18/01/2024</t>
+  </si>
+  <si>
+    <t>5608714230</t>
   </si>
   <si>
     <t>PDI Eletrônico - Atividade IV</t>
@@ -171,13 +180,13 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>23260</t>
+    <t>5610879368</t>
   </si>
   <si>
     <t>Data Retorno Usinagem</t>
   </si>
   <si>
-    <t>23603</t>
+    <t>5695885983</t>
   </si>
   <si>
     <t>Registro de Pintura da Macharia</t>
@@ -186,19 +195,25 @@
     <t>15/12/2023</t>
   </si>
   <si>
-    <t>23567</t>
+    <t>15/01/2024</t>
+  </si>
+  <si>
+    <t>5695976808</t>
   </si>
   <si>
     <t>Inclusão do Forno X nos relatórios do sistema de Corrida</t>
   </si>
   <si>
-    <t>23560</t>
+    <t>5695998982</t>
   </si>
   <si>
     <t>Reexportação de NFS com retenção</t>
   </si>
   <si>
-    <t>23177</t>
+    <t>16/01/2024</t>
+  </si>
+  <si>
+    <t>5703792350</t>
   </si>
   <si>
     <t>Controle de saídas no embarque</t>
@@ -207,88 +222,94 @@
     <t>18/12/2023</t>
   </si>
   <si>
-    <t>23485</t>
+    <t>5702761161</t>
   </si>
   <si>
     <t>Estorno de peças do deposito fabril  - Incorporar modelo</t>
   </si>
   <si>
+    <t>5703009879</t>
+  </si>
+  <si>
     <t>Estorno de peças do deposito fabril - Webservice Estorno (Implantação)</t>
   </si>
   <si>
-    <t>23482</t>
+    <t>5608641165</t>
   </si>
   <si>
     <t>Alteração consulta de corridas</t>
   </si>
   <si>
+    <t>11/01/2024</t>
+  </si>
+  <si>
     <t>5818995481</t>
   </si>
   <si>
     <t>Movimentação Retroativa Registro de Inspeção - Analise</t>
   </si>
   <si>
-    <t>23393</t>
+    <t>5610440885</t>
   </si>
   <si>
     <t>Cadastro de analistas de vendas</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>5819096063</t>
   </si>
   <si>
     <t>Produtivo em horas - Conversão rotina para EV3</t>
   </si>
   <si>
-    <t>23391</t>
+    <t>5610450402</t>
   </si>
   <si>
     <t>Novas opções de classificação de cliente</t>
   </si>
   <si>
-    <t>23767</t>
+    <t>5706679265</t>
   </si>
   <si>
     <t>Colocar Icone de lixeira sequência na área de criação de OM</t>
   </si>
   <si>
-    <t>23917</t>
+    <t>5813848014</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Exportação Imobilizado para Benner</t>
   </si>
   <si>
-    <t>23906</t>
+    <t>5813869025</t>
   </si>
   <si>
     <t>RELATÓRIOS SISTEMA DE INVOICE - TICKETS</t>
   </si>
   <si>
-    <t>23870</t>
+    <t>5813941982</t>
   </si>
   <si>
     <t>Inserir nova coluna na máscara MPS</t>
   </si>
   <si>
-    <t>23833</t>
+    <t>5814010807</t>
   </si>
   <si>
     <t>Melhorias para os filtros de seleção 'Planilha do excel'</t>
   </si>
   <si>
-    <t>23790</t>
+    <t>5814038746</t>
   </si>
   <si>
     <t>Bloqueio de nota cancelada/recusada/de outros clientes</t>
   </si>
   <si>
-    <t>23788</t>
+    <t>5814050194</t>
   </si>
   <si>
     <t>Apontamento incorreto no sistema</t>
   </si>
   <si>
-    <t>23754</t>
+    <t>5814070685</t>
   </si>
   <si>
     <t>ajustes posto de cópia eletrônico.</t>
@@ -300,7 +321,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-27</t>
+    <t>Nov/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -1036,24 +1057,24 @@
         <v>35</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1065,13 +1086,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1080,10 +1101,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1100,25 +1121,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>21</v>
@@ -1127,10 +1148,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1139,7 +1160,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1147,25 +1168,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>21</v>
@@ -1174,10 +1195,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1186,15 +1207,15 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1206,42 +1227,42 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="O9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1253,13 +1274,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>21</v>
@@ -1268,10 +1289,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1280,15 +1301,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1300,13 +1321,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1315,10 +1336,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1327,15 +1348,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1347,13 +1368,13 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>21</v>
@@ -1362,10 +1383,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1374,30 +1395,30 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -1409,10 +1430,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1421,15 +1442,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1441,13 +1462,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>21</v>
@@ -1456,10 +1477,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1468,15 +1489,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1488,13 +1509,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1503,10 +1524,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1515,15 +1536,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1535,13 +1556,13 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1550,10 +1571,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1562,15 +1583,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1582,13 +1603,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -1600,7 +1621,7 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1617,7 +1638,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1629,13 +1650,13 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1644,10 +1665,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1656,33 +1677,33 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -1694,7 +1715,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1711,7 +1732,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1723,13 +1744,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>21</v>
@@ -1738,10 +1759,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1750,33 +1771,33 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1785,7 +1806,7 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>24</v>
@@ -1797,15 +1818,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1817,13 +1838,13 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>21</v>
@@ -1832,10 +1853,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1852,7 +1873,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1864,13 +1885,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -1879,10 +1900,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1899,7 +1920,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1911,13 +1932,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -1926,10 +1947,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1946,7 +1967,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -1958,13 +1979,13 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -1973,10 +1994,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -1993,7 +2014,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2005,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2020,10 +2041,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2040,7 +2061,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2052,13 +2073,13 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2067,10 +2088,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2087,7 +2108,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2099,13 +2120,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2114,10 +2135,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2145,23 +2166,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2169,16 +2190,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2189,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>23.41</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2197,7 +2218,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2210,7 +2231,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2218,7 +2239,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2249,12 +2270,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B2">
         <v>27</v>
@@ -2268,7 +2289,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2278,25 +2299,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2313,13 +2334,13 @@
         <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2331,15 +2352,15 @@
         <v>26</v>
       </c>
       <c r="P10" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -2357,19 +2378,19 @@
         <v>27</v>
       </c>
       <c r="M11" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="Q11">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>17</v>
       </c>
@@ -2377,39 +2398,33 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12">
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
-      <c r="P12" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q12">
-        <v>9</v>
-      </c>
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2423,7 +2438,7 @@
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -2431,7 +2446,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2439,7 +2454,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2447,7 +2462,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2455,10 +2470,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2466,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2480,7 +2495,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -2494,7 +2509,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -2508,7 +2523,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -2516,100 +2531,100 @@
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
